--- a/sensor_data.xlsx
+++ b/sensor_data.xlsx
@@ -425,88 +425,143 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>sensor_id</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>sensor_target</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>parameter</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>datetimeFirst</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>datetimeLast</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>coverage</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>latest</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>summary</t>
+          <t>units</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
+        <v>3916</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>no2</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>ppm</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>3918</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>so2</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>ppm</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3920</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>pm25</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>µg/m³</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
         <v>3917</v>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>o3 ppm</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>{'id': 10, 'name': 'o3', 'units': 'ppm', 'displayName': 'O₃'}</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>{'utc': '2016-03-06T20:00:00Z', 'local': '2016-03-06T13:00:00-07:00'}</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>{'utc': '2026-01-09T17:00:00Z', 'local': '2026-01-09T10:00:00-07:00'}</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>{'expectedCount': 1, 'expectedInterval': '01:00:00', 'observedCount': 68574, 'observedInterval': '68574:00:00', 'percentComplete': 6857400.0, 'percentCoverage': 6857400.0, 'datetimeFrom': {'utc': '2016-03-06T20:00:00Z', 'local': '2016-03-06T13:00:00-07:00'}, 'datetimeTo': {'utc': '2026-01-09T17:00:00Z', 'local': '2026-01-09T10:00:00-07:00'}}</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>{'datetime': {'utc': '2026-01-09T17:00:00Z', 'local': '2026-01-09T10:00:00-07:00'}, 'value': 0.036, 'coordinates': {'latitude': 35.1353, 'longitude': -106.584702}}</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>{'min': 0.0, 'q02': None, 'q25': None, 'median': None, 'q75': None, 'q98': None, 'max': 0.109, 'avg': 0.03580498661195457, 'sd': None}</t>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>o3</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>ppm</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>3919</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>pm10</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>µg/m³</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>25227</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>co</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>ppm</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>4272103</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>nox</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>ppm</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>4272226</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>ppm</t>
         </is>
       </c>
     </row>

--- a/sensor_data.xlsx
+++ b/sensor_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -535,36 +535,6 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>4272103</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>nox</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>ppm</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>4272226</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>ppm</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/sensor_data.xlsx
+++ b/sensor_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -460,81 +460,6 @@
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>3918</v>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>so2</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>ppm</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>3920</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>pm25</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>µg/m³</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>3917</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>o3</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>ppm</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>3919</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>pm10</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>µg/m³</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>25227</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>co</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>ppm</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/sensor_data.xlsx
+++ b/sensor_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -460,6 +460,111 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>3918</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>so2</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>ppm</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3920</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>pm25</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>µg/m³</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3917</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>o3</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>ppm</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>3919</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>pm10</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>µg/m³</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>25227</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>co</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>ppm</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>4272103</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>nox</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>ppm</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>4272226</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>ppm</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/sensor_data.xlsx
+++ b/sensor_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -460,111 +460,6 @@
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>3918</v>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>so2</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>ppm</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>3920</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>pm25</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>µg/m³</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>3917</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>o3</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>ppm</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>3919</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>pm10</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>µg/m³</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>25227</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>co</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>ppm</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>4272103</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>nox</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>ppm</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>4272226</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>ppm</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/sensor_data.xlsx
+++ b/sensor_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -460,6 +460,96 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>3918</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>so2</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>ppm</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3920</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>pm25</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>µg/m³</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3917</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>o3</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>ppm</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>3919</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>pm10</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>µg/m³</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>25227</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>co</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>ppm</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>4272103</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>nox</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>ppm</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/sensor_data.xlsx
+++ b/sensor_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -550,6 +550,21 @@
         </is>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>4272226</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>ppm</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
